--- a/mario/ops/cvxlab_models/Split_sut_act/model_settings.xlsx
+++ b/mario/ops/cvxlab_models/Split_sut_act/model_settings.xlsx
@@ -1857,7 +1857,7 @@
     <row r="2">
       <c r="B2" t="inlineStr">
         <is>
-          <t>Minimize(sum(entropy(U_pn,U0_pn))+sum(entropy(M_pn,M0_pn))+sum(entropy(V_pn,V0_pn)))</t>
+          <t>Minimize(sum(entropy(U_pn,U0_pn))+sum(entropy(M_pn,M0_pn))+sum(entropy_signed(V_pn,V0_pn)))</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1941,7 +1941,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vold_p_r&lt;=(V_pn_r@I_act_p_pn@I_a_from_to_p)*(1+eps)</t>
+          <t>Vold_p_r-absval(Vold_p_r)*eps&lt;=(V_pn_r@I_act_p_pn@I_a_from_to_p)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1953,7 +1953,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vold_p_r&gt;=(V_pn_r@I_act_p_pn@I_a_from_to_p)*(1-eps)</t>
+          <t>Vold_p_r+absval(Vold_p_r)*eps&gt;=(V_pn_r@I_act_p_pn@I_a_from_to_p)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
